--- a/preprocessing/headlines_dataset_15sample_LLM.xlsx
+++ b/preprocessing/headlines_dataset_15sample_LLM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\infoling2\frame_detect_NLP\preprocessing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63720051-279B-48F7-8DE7-42CB6F62BF15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36D117FF-5DCC-4EAA-8806-5A6E39C25EDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="436" uniqueCount="231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="647" uniqueCount="442">
+  <si>
+    <t>Filename</t>
+  </si>
   <si>
     <t>Headline_GER</t>
   </si>
@@ -70,646 +73,1276 @@
     <t>External regulation and reputation</t>
   </si>
   <si>
+    <t>article761874505.txt</t>
+  </si>
+  <si>
     <t>Von Trump begnadigter Ex-Seemann sagt, er verklage Obama und Comey</t>
   </si>
   <si>
     <t>en</t>
   </si>
   <si>
+    <t>article999001226.txt</t>
+  </si>
+  <si>
     <t>Brenda Snipes, Wahlleiterin im Broward County, tritt wegen Wahlbetrugs in Florida zurück</t>
   </si>
   <si>
+    <t>article790720714.txt</t>
+  </si>
+  <si>
     <t>Ich sage, was Kavanaugh nicht sagen würde: Christine Ford war Teil des politischen Anschlags auf ihn und hier ist der Audiobeweis</t>
   </si>
   <si>
+    <t>article709732928.txt</t>
+  </si>
+  <si>
     <t>Uranium One Bombshell: Beweise für Bestechung, Erpressung, Schmiergelder, Geldwäsche und mehr!</t>
   </si>
   <si>
+    <t>article999001256.txt</t>
+  </si>
+  <si>
     <t>Schlechter Verlierer: Stacey Abrams beendet Herausforderungen im Rennen um den Gouverneursposten in Georgia – wird nicht zugeben – will Klage einreichen</t>
   </si>
   <si>
+    <t>article702077783.txt</t>
+  </si>
+  <si>
     <t>Lokale Polizei und Fed verhängen Informationssperre bei Schießerei in Las Vegas</t>
   </si>
   <si>
+    <t>article729410793.txt</t>
+  </si>
+  <si>
     <t>Deutscher Kardinal: Liturgischer „Segen“ für Schwulengemeinschaften ist „wirklich … Sakrileg“</t>
   </si>
   <si>
+    <t>article999001323.txt</t>
+  </si>
+  <si>
     <t>Das Gericht ordnet an, dass das Weiße Haus die Presseberechtigung des CNN-Korrespondenten Jim Acosta wiederherstellen muss</t>
   </si>
   <si>
+    <t>article764715911.txt</t>
+  </si>
+  <si>
     <t>Nachdem die American Medical Association die Beschlagnahmung von Waffen und Munition sowie die allgemeine Waffenregistrierung gefordert hat, sollte sie darüber nachdenken, „amerikanisch“ aus ihrem Namen zu streichen</t>
   </si>
   <si>
+    <t>article737194975.txt</t>
+  </si>
+  <si>
     <t>Hat Trump die Tür geöffnet?</t>
   </si>
   <si>
+    <t>article999001290.txt</t>
+  </si>
+  <si>
     <t>Richter befiehlt dem Weißen Haus, den Presseausweis von Jim Acosta wiederherzustellen – Trump antwortet</t>
   </si>
   <si>
+    <t>article771879020.txt</t>
+  </si>
+  <si>
     <t>DOJ kapituliert: 3D-Druck-Waffenakten sind durch den ersten Verfassungszusatz geschützt</t>
   </si>
   <si>
+    <t>article758669180.txt</t>
+  </si>
+  <si>
     <t>Die USA warnen vor „Schallangriffen“ in China</t>
   </si>
   <si>
+    <t>article111111112.txt</t>
+  </si>
+  <si>
     <t>US-Bloggern wurde die Einreise nach Großbritannien verboten</t>
   </si>
   <si>
+    <t>article813953273.txt</t>
+  </si>
+  <si>
     <t>RICHARD LITTLEJOHN: In der Hauptstadt kommt es zum ersten Mal in diesem Jahr zu Messerstechereien</t>
   </si>
   <si>
+    <t>article764664283.txt</t>
+  </si>
+  <si>
     <t>Gary Wills, Autor der törichten Religion: „Die Religion des Korans ist eine Religion des Friedens“</t>
   </si>
   <si>
+    <t>article833050243.txt</t>
+  </si>
+  <si>
     <t>Mueller-Bericht: „Die USA haben die EU gezwungen, ihre Sanktionen ohne Beweise durchzusetzen“</t>
   </si>
   <si>
+    <t>article817449755.txt</t>
+  </si>
+  <si>
     <t>Derbyshire jubelt über harten Brexit | Blogbeiträge</t>
   </si>
   <si>
+    <t>article725498022.txt</t>
+  </si>
+  <si>
     <t>SONDERBERICHT: Papst Franziskus wird Untätigkeit in Fällen berüchtigten sexuellen Missbrauchs vorgeworfen</t>
   </si>
   <si>
+    <t>article728153988.txt</t>
+  </si>
+  <si>
     <t>Illegaler Ausländer, der wegen versuchten Mordes in North Carolina gesucht wird, an der Grenze zwischen den USA und Mexiko festgenommen</t>
   </si>
   <si>
+    <t>article730246508.txt</t>
+  </si>
+  <si>
     <t>Mann wurde verhaftet, weil er am Tatort des 911-Auflegens angeblich eine Waffe gekauft hatte, mit der Polizisten aus Ohio getötet wurden</t>
   </si>
   <si>
+    <t>article729651527.txt</t>
+  </si>
+  <si>
     <t>Student sagt, Antisemitismus sei immer noch ein Problem in der McGill-Studentenregierung</t>
   </si>
   <si>
+    <t>article757713354.txt</t>
+  </si>
+  <si>
     <t>Nicht so schnell</t>
   </si>
   <si>
+    <t>article729581752.txt</t>
+  </si>
+  <si>
     <t>Die Sonne wird kühler und schwächer, aber die Wissenschaftler machen sich keine Sorgen</t>
   </si>
   <si>
+    <t>article701299732.txt</t>
+  </si>
+  <si>
     <t>Es ist in der Luft: Beamte warnen, dass sich die Seuche „Schwarzer Tod“ schnell ausbreiten könnte</t>
   </si>
   <si>
+    <t>article738028498.txt</t>
+  </si>
+  <si>
     <t>Ist die Auslöschung der Menschheit vorhersehbar? Weltgesundheitschef: Globale Pandemie steht unmittelbar bevor</t>
   </si>
   <si>
+    <t>article833040400.txt</t>
+  </si>
+  <si>
     <t>Mueller-Bericht wird am Samstag von A.G. Barr geprüft</t>
   </si>
   <si>
+    <t>article779394730.txt</t>
+  </si>
+  <si>
     <t>Hunderte Priester in Pennsylvania angeklagt, Begleitkirche in der Krise</t>
   </si>
   <si>
+    <t>article770156851.txt</t>
+  </si>
+  <si>
     <t>Die Never-Trumpers kommen niemals zurück</t>
   </si>
   <si>
+    <t>article764609985.txt</t>
+  </si>
+  <si>
     <t>Clintons E-Mail-IG-Bericht zerreißt FBI, Comey und Lynch … und noch viel mehr!</t>
   </si>
   <si>
+    <t>article735855251.txt</t>
+  </si>
+  <si>
     <t>ICE verhaftet 20 Personen in Kansas City während einer viertägigen Operation gegen kriminelle Ausländer</t>
   </si>
   <si>
+    <t>article765982381.txt</t>
+  </si>
+  <si>
     <t>Julian Assange</t>
   </si>
   <si>
+    <t>article705409419.txt</t>
+  </si>
+  <si>
     <t>﻿Vatikanischer Theologe entlassen, weil er das Pontifikat des „barmherzigen“ Papstes in Frage gestellt hat</t>
   </si>
   <si>
+    <t>article813949697.txt</t>
+  </si>
+  <si>
     <t>Die Polizei bereitet sich auf den Einsatz in Nordirland für den Fall eines No-Deal-Brexit vor</t>
   </si>
   <si>
+    <t>article833028680.txt</t>
+  </si>
+  <si>
     <t>Mueller verstehen: Was Sie über den Bericht zur Russland-Untersuchung wissen müssen</t>
   </si>
   <si>
+    <t>article785331076.txt</t>
+  </si>
+  <si>
     <t>Texas: Polizist betritt das Haus, von dem sie dachte, es gehöre ihr, und tötet einen unschuldigen Hausbesitzer – wird aber nicht verhaftet</t>
   </si>
   <si>
+    <t>article999000675.txt</t>
+  </si>
+  <si>
     <t>Demokratenfreund Louis Farrakhan im Iran: „Tod für Amerika!“ – Amerika ist der „große Satan“</t>
   </si>
   <si>
+    <t>article730389374.txt</t>
+  </si>
+  <si>
     <t>Amerikas Einwanderungsstimme.</t>
   </si>
   <si>
+    <t>article833028932.txt</t>
+  </si>
+  <si>
     <t>Der Mueller-Bericht wird endlich fallen gelassen, die Demokraten bereiten eine Liste mit Forderungen vor</t>
   </si>
   <si>
+    <t>article723844295.txt</t>
+  </si>
+  <si>
     <t>Gesetzgeber macht schockierende Behauptung zum Massaker in Las Vegas (Video)</t>
   </si>
   <si>
+    <t>article786250729.txt</t>
+  </si>
+  <si>
     <t>Google hat mit Clintons Wahlkampf mit „stillen Spenden“ zusammengearbeitet</t>
   </si>
   <si>
+    <t>article833021113.txt</t>
+  </si>
+  <si>
     <t>Jerome Corsi, Mitarbeiter von Roger Stone, feiert das Ende der Mueller-Untersuchung, nachdem er sich geweigert hat, einen Plädoyervertrag zu unterzeichnen</t>
   </si>
   <si>
+    <t>article710376094.txt</t>
+  </si>
+  <si>
     <t>Asteroid wird wenige Tage vor Weihnachten an der Erde vorbeifliegen: Er ist „potenziell gefährlich“</t>
   </si>
   <si>
+    <t>article832933796.txt</t>
+  </si>
+  <si>
     <t>Trump-Berater optimistisch: Mueller „hat nicht das Zeug dazu“</t>
   </si>
   <si>
+    <t>article786731884.txt</t>
+  </si>
+  <si>
     <t>Facebook-Verbotsentwurf zur Verhinderung dschihadistischer Angriffe auf Amerikaner.</t>
   </si>
   <si>
+    <t>article761568202.txt</t>
+  </si>
+  <si>
     <t>Bill Clinton: „Ich habe das Richtige getan“ während der Lewinsky-Affäre; „Ich schulde ihr keine Entschuldigung.“</t>
   </si>
   <si>
+    <t>article833041409.txt</t>
+  </si>
+  <si>
     <t>Beto O'Rourke sagt, er glaube immer noch, dass Trump mit Russland konspiriert habe</t>
   </si>
   <si>
+    <t>article833039623.txt</t>
+  </si>
+  <si>
     <t>Robert Mueller III lässt seinen Fall ruhen – die Demokraten werden es NIEMALS tun</t>
   </si>
   <si>
+    <t>article763114850.txt</t>
+  </si>
+  <si>
     <t>Wer steckt hinter der Internet-Gedankenpolizei?</t>
   </si>
   <si>
+    <t>article999000142.txt</t>
+  </si>
+  <si>
     <t>Hillary macht einen rassistischen Witz, nachdem sie Cory Booker und Eric Holder verwechselt hat: „Sie sehen alle gleich aus“</t>
   </si>
   <si>
+    <t>article111111122.txt</t>
+  </si>
+  <si>
     <t>Kavanaughs Nominierung explodiert vor Trumps Gesicht</t>
   </si>
   <si>
+    <t>article733754480.txt</t>
+  </si>
+  <si>
     <t>Brasilianischer Waffenhändler in den USA festgenommen</t>
   </si>
   <si>
+    <t>article999000565.txt</t>
+  </si>
+  <si>
     <t>Anschauen: Campus Commie hat einen mit Obszönitäten beladenen, zischenden Anfall und schüttet Getränke über FSU-Republikaner aus</t>
   </si>
   <si>
+    <t>article832956618.txt</t>
+  </si>
+  <si>
     <t>Mueller ist fertig, aber die Trump-Ermittlungen nehmen nur noch Fahrt auf</t>
   </si>
   <si>
+    <t>article999001259.txt</t>
+  </si>
+  <si>
     <t>Obama-Richter entscheidet, Wahl in Georgia zu ändern</t>
   </si>
   <si>
+    <t>article833024696.txt</t>
+  </si>
+  <si>
     <t>Die Demokraten von 2020 fordern die Veröffentlichung des Mueller-Berichts</t>
   </si>
   <si>
+    <t>article813547724.txt</t>
+  </si>
+  <si>
     <t>Außenminister Jeremy Hunt sagt, Großbritannien dürfe „seine Stärke“ nach dem Brexit nicht unterschätzen</t>
   </si>
   <si>
+    <t>article758472954.txt</t>
+  </si>
+  <si>
     <t>Hüten Sie sich vor Angriffen mit Schallwaffen, sagen die USA den Bürgern in China</t>
   </si>
   <si>
+    <t>article770156173.txt</t>
+  </si>
+  <si>
     <t>Beende den Koreakrieg!</t>
   </si>
   <si>
+    <t>article704591553.txt</t>
+  </si>
+  <si>
     <t>Eine antisemitische Säuberung an der McGill University</t>
   </si>
   <si>
+    <t>article737457870.txt</t>
+  </si>
+  <si>
     <t>Dritthöchster demokratischer Bürgerrechtsheld erschien mit Farrakhan, wird nicht verurteilen</t>
   </si>
   <si>
+    <t>article727869189.txt</t>
+  </si>
+  <si>
     <t>Papst Franziskus: Ross Douthat und Massimo Faggioli diskutieren über die Zukunft der katholischen Kirche</t>
   </si>
   <si>
+    <t>article722512241.txt</t>
+  </si>
+  <si>
     <t>Ehemalige muslimische Katholiken an Papst Franziskus: „Naivität gegenüber dem Islam ist selbstmörderisch und sehr gefährlich“</t>
   </si>
   <si>
+    <t>article833067493.txt</t>
+  </si>
+  <si>
     <t>Don Trump Jr. nutzt das Vaterschafts-Mem von Maury Povich, um sich über die Demokraten lustig zu machen</t>
   </si>
   <si>
+    <t>article814777937.txt</t>
+  </si>
+  <si>
     <t>Die extreme Rechte versucht, die Gelbwesten zu vereinnahmen</t>
   </si>
   <si>
+    <t>article763260610.txt</t>
+  </si>
+  <si>
     <t>Die unheimliche Stille</t>
   </si>
   <si>
+    <t>article820791520.txt</t>
+  </si>
+  <si>
     <t>Georg III. hat Amerika verloren.</t>
   </si>
   <si>
+    <t>article789121798.txt</t>
+  </si>
+  <si>
     <t>Skeptisch gegenüber dokumentierten Lügnern zu sein, die einen Kandidaten für den Obersten Gerichtshof angreifen, ist eine gute Sache – hier ist der Grund dafür</t>
   </si>
   <si>
+    <t>article730573740.txt</t>
+  </si>
+  <si>
     <t>Kardinal Müller: Die Segnung homosexueller Paare wäre eine „Gräueltat“</t>
   </si>
   <si>
+    <t>article813452859.txt</t>
+  </si>
+  <si>
     <t>EU profitiert vom Handel mit Großbritannien, während London Geld verliert – politischer Aktivist</t>
   </si>
   <si>
+    <t>article813953435.txt</t>
+  </si>
+  <si>
     <t>Die Mehrheit der Tory-Wähler möchte, dass ihre Abgeordneten den Deal von Theresa May unterstützen</t>
   </si>
   <si>
+    <t>article732708002.txt</t>
+  </si>
+  <si>
     <t>Die von Rücktritten und Kritik betroffene Kommission für sexuellen Missbrauch von Papst Franziskus erhält einen Neustart</t>
   </si>
   <si>
+    <t>article815412286.txt</t>
+  </si>
+  <si>
     <t>Ex-MI6-Chef sagt, Theresa Mays Brexit-Deal „bedroht die nationale Sicherheit“ und schadet den Beziehungen zu den USA</t>
   </si>
   <si>
+    <t>article696264594.txt</t>
+  </si>
+  <si>
     <t>Die American Jewish Historical Society veranstaltet die Veranstaltung „Zerstöre Israel“.</t>
   </si>
   <si>
+    <t>article761546223.txt</t>
+  </si>
+  <si>
     <t>Homeschooling schützt Kinder vor Gewalt und Marxismus</t>
   </si>
   <si>
+    <t>article695108099.txt</t>
+  </si>
+  <si>
     <t>Aus der Quittung geht hervor, dass Paddock vor den Dreharbeiten einen weiteren Gast in seinem Zimmer hatte</t>
   </si>
   <si>
+    <t>article833052347.txt</t>
+  </si>
+  <si>
     <t>Die USA reagieren mit Erleichterung und Skepsis auf das Ende der Mueller-Untersuchung</t>
   </si>
   <si>
+    <t>article2329.txt</t>
+  </si>
+  <si>
     <t>Unterstützen westliche Spione die neuen „ukrainischen Weißhelme“?</t>
   </si>
   <si>
     <t>fr</t>
   </si>
   <si>
+    <t>article2348.txt</t>
+  </si>
+  <si>
     <t>Zwischen Wladimir Putin und dem Westen geht die Pattsituation weiter</t>
   </si>
   <si>
+    <t>article23100.txt</t>
+  </si>
+  <si>
     <t>Franziskus, Papst der Armen und der Ökologie? Oder Papst der globalen Elite?</t>
   </si>
   <si>
+    <t>article2396.txt</t>
+  </si>
+  <si>
     <t>Joe Biden und die G-7 wollen Milliarden von Dollar ausgeben, um „grüne Projekte“ in der Dritten Welt zu finanzieren</t>
   </si>
   <si>
+    <t>article23209.txt</t>
+  </si>
+  <si>
     <t>Kampf gegen Homophobie: Noch in diesem Jahr werde ein „Botschafter für LGBT+-Rechte“ ernannt, kündigt Elisabeth Borne an</t>
   </si>
   <si>
+    <t>article23175.txt</t>
+  </si>
+  <si>
     <t>Das Verteidigungsministerium der Russischen Föderation veröffentlichte Daten über die Arbeit mit Zeckeninfektionen in biologischen Labors der Vereinigten Staaten in der Ukraine</t>
   </si>
   <si>
+    <t>article2347.txt</t>
+  </si>
+  <si>
     <t>Ukraine – Russische Rakete, die auf Zivilisten zielt, tötet versehentlich mehrere ukrainische Soldaten</t>
   </si>
   <si>
+    <t>article23106.txt</t>
+  </si>
+  <si>
     <t>Eine „City COP“ zur Bekämpfung des Klimawandels</t>
   </si>
   <si>
+    <t>article238.txt</t>
+  </si>
+  <si>
     <t>Biden nennt MAGA-Ideologie „extrem“</t>
   </si>
   <si>
+    <t>article2345.txt</t>
+  </si>
+  <si>
     <t>Eine beispielhafte Sanktion, die von unseren fantastisch intelligenten Führern fachmännisch untersucht wurde!!!</t>
   </si>
   <si>
+    <t>article2379.txt</t>
+  </si>
+  <si>
     <t>Für 2060 wird ein monströser Plastikberg vorhergesagt</t>
   </si>
   <si>
+    <t>article23104.txt</t>
+  </si>
+  <si>
     <t>„Die Klimastrategie der Europäischen Union soll die Entwaldung weltweit verstärken“</t>
   </si>
   <si>
+    <t>article2399.txt</t>
+  </si>
+  <si>
     <t>Macron will die Ungeimpften „verärgern“: eine erschreckende totalitäre Wende</t>
   </si>
   <si>
+    <t>article2336.txt</t>
+  </si>
+  <si>
     <t>Das WEF möchte, dass Kinder im Metaversum lernen, den Klimawandel zu bekämpfen</t>
   </si>
   <si>
+    <t>article232.txt</t>
+  </si>
+  <si>
     <t>Umweltfanatismus: Aktuelle Nachrichten aus Europa</t>
   </si>
   <si>
+    <t>article2323.txt</t>
+  </si>
+  <si>
     <t>Die NATO und Russland tun so, als hätten sie keine Angst</t>
   </si>
   <si>
+    <t>article23198.txt</t>
+  </si>
+  <si>
     <t>Nachhaltiger Olympismus</t>
   </si>
   <si>
+    <t>article23134.txt</t>
+  </si>
+  <si>
     <t>Was wäre, wenn Frankreich Amerikanern, die eine Abtreibung wünschen, Asyl anbieten würde?</t>
   </si>
   <si>
+    <t>article23140.txt</t>
+  </si>
+  <si>
     <t>Zentralbanken kontrollieren die Inflation nicht</t>
   </si>
   <si>
+    <t>article23204.txt</t>
+  </si>
+  <si>
     <t>Klima – Forscher entwickeln einen Sonnenschutz mit Index 450</t>
   </si>
   <si>
+    <t>article23197.txt</t>
+  </si>
+  <si>
     <t>Weitere dreißig Jahre verloren</t>
   </si>
   <si>
+    <t>article23164.txt</t>
+  </si>
+  <si>
     <t>Angesichts des gesetzlosen Lügners kämpfte Marine gut</t>
   </si>
   <si>
+    <t>article23172.txt</t>
+  </si>
+  <si>
     <t>Alle gesundheitspolitischen Entscheidungen von Emmanuel Macron haben mehr als 600 Milliarden gekostet, für welches Ergebnis?</t>
   </si>
   <si>
+    <t>article2370.txt</t>
+  </si>
+  <si>
     <t>Die Minsker Abkommen, welche Minsker Abkommen?</t>
   </si>
   <si>
+    <t>article23177.txt</t>
+  </si>
+  <si>
     <t>[Ukraine] Warum ist Russland nicht vom Rest der Welt isoliert?</t>
   </si>
   <si>
+    <t>article2373.txt</t>
+  </si>
+  <si>
     <t>Katastrophe und Panik</t>
   </si>
   <si>
+    <t>article2313.txt</t>
+  </si>
+  <si>
     <t>Russisches Staatsfernsehen beruhigt Zuschauer vor Atomkrieg: „Eines Tages werden wir alle sterben“</t>
   </si>
   <si>
+    <t>article2383.txt</t>
+  </si>
+  <si>
     <t>Klima: Frankreich ist für künftige Krisen schlecht gerüstet</t>
   </si>
   <si>
+    <t>article2363.txt</t>
+  </si>
+  <si>
     <t>Wladimir Putin schickt seine Armee in den Mittelpunkt der Erde, um „die Lava zu entnazifizieren“</t>
   </si>
   <si>
+    <t>article23208.txt</t>
+  </si>
+  <si>
     <t>Aus Texas fordert Viktor Orban die amerikanischen Konservativen auf, angesichts des von der Linken geführten „Kulturkrieges“ „ihre Kräfte zu bündeln“.</t>
   </si>
   <si>
+    <t>article23188.txt</t>
+  </si>
+  <si>
     <t>Vereinigte Staaten: Nicht alles ist ein nationaler Notfall</t>
   </si>
   <si>
+    <t>article23184.txt</t>
+  </si>
+  <si>
     <t>Taiwan: Xi Jinping fordert Joe Biden auf, nicht „mit dem Feuer zu spielen“</t>
   </si>
   <si>
+    <t>article2268.txt</t>
+  </si>
+  <si>
     <t>UN-Kommissar Filippo Grandi weist auf Doppelmoral bei Behandlung von Flüchtlingen hin</t>
   </si>
   <si>
     <t>ge</t>
   </si>
   <si>
+    <t>article22135.txt</t>
+  </si>
+  <si>
     <t>Geheimer NATO-Bericht via Wikileaks zeigte miserable russische Streitkräfte, Drang zu taktischen Atomwaffen</t>
   </si>
   <si>
+    <t>article2270.txt</t>
+  </si>
+  <si>
     <t>Westliche Sanktionen bewirken das Gegenteil: Rußlands Energie-Einnahmen höher als vor dem Krieg</t>
   </si>
   <si>
+    <t>article2246.txt</t>
+  </si>
+  <si>
     <t>Der Ukrainer nutzt den Krieg und die Faschisten, um sich an der Macht zu halten. Preisfrage: Wann lief die letzte 20-Uhr-Tagesschau ohne Beitrag über Ukraines Präsidenten Selenskyj – albern kostümiert in NATO-Oliv, Waffen und Geld fordernd? „Selenskyj“ im Suchfeld auf tagesschau.de ergibt für die letzten drei Monate mehr als 1 400 Treffer. Tagesschau.de listet darunter mehr als 500-mal Selenskyj-Videos: Heldenverehrung für einen ferngesteuerten Gewaltherrscher, der den Kriegszustand zur Festigung der eigenen Position verlängert und dafür täglich hunderte Menschenleben opfert. Hingegen verschwieg die Tagesschau den weltweit beachteten Rat des einstigen US-Außenministers Henry Kissinger, Selenskyj solle zur Vermeidung einer gesamteuropäischen Katastrophe freiwillig Territorium an Russland abtreten und Frieden schließen. Kissingers Realismus passte der giftgrün-linientreuen ARD-aktuell-Redaktion ersichtlich nicht in den Propagandakram.</t>
   </si>
   <si>
+    <t>article2248.txt</t>
+  </si>
+  <si>
     <t>Umfrage deckt auf: 83 Prozent der Deutschen wünschen sich besseren Grenzschutz</t>
   </si>
   <si>
+    <t>article22132.txt</t>
+  </si>
+  <si>
     <t>Bis 380 US-Dollar pro Barrel: Experten warnen von dramatischen Erdölpreissteigerungen</t>
   </si>
   <si>
+    <t>article22187.txt</t>
+  </si>
+  <si>
     <t>Victor in Amerika</t>
   </si>
   <si>
+    <t>article2298.txt</t>
+  </si>
+  <si>
     <t>Mit Marine Le Pen übernimmt eine Rechtspopulistin die Fraktionsführung</t>
   </si>
   <si>
+    <t>article227.txt</t>
+  </si>
+  <si>
     <t>Energiepolitik: Wasserstoff ist als klimafreundlicher Energieträger fragwürdig</t>
   </si>
   <si>
+    <t>article2282.txt</t>
+  </si>
+  <si>
     <t>Religiöse Führer sagen, dass Covid-Impfungen für den Anstieg von „dämonischen Besessenheit“ verantwortlich ist</t>
   </si>
   <si>
+    <t>article226.txt</t>
+  </si>
+  <si>
     <t>WHO-Impfkampagne mit fatalen Folgen: Immer mehr Fälle von „Impf-Polio” in Afrika</t>
   </si>
   <si>
+    <t>article2240.txt</t>
+  </si>
+  <si>
     <t>Klimawandel: Wie der „Spiegel“ zu linker Gewalt aufruft</t>
   </si>
   <si>
+    <t>article22175.txt</t>
+  </si>
+  <si>
     <t>"Gas gibt es gar nicht. Es ist eine Erfindung der Regierung" – Querheizer sieht Winter entspannt entgegen</t>
   </si>
   <si>
+    <t>article2257.txt</t>
+  </si>
+  <si>
     <t>Maske oder nicht? Sei wie Cem, Justin, Markus und Co!</t>
   </si>
   <si>
+    <t>article2213.txt</t>
+  </si>
+  <si>
     <t>Die Nato allein zuhaus</t>
   </si>
   <si>
+    <t>article2262.txt</t>
+  </si>
+  <si>
     <t>Wer archaische Traditionen zu unserem Alltag machen will, hat Deutschland zu verlassen!</t>
   </si>
   <si>
+    <t>article22192.txt</t>
+  </si>
+  <si>
     <t>Putins Werk und Kyrills Beitrag</t>
   </si>
   <si>
+    <t>article2289.txt</t>
+  </si>
+  <si>
     <t>Eine neue Kirche, ein neuer Glauben, ein neues Volk</t>
   </si>
   <si>
+    <t>article2294.txt</t>
+  </si>
+  <si>
     <t>Prüderie statt Pride</t>
   </si>
   <si>
+    <t>article2238.txt</t>
+  </si>
+  <si>
     <t>Davos: „Klima-Schützer“ fliegen mit 1.500 (!) Privatjets ein</t>
   </si>
   <si>
+    <t>article2244.txt</t>
+  </si>
+  <si>
     <t>Global Health Governance ist eines der grundlegenden Elemente der Neuen Weltordnung und muss als solches abgelehnt und bekämpft werden.</t>
   </si>
   <si>
+    <t>article22130.txt</t>
+  </si>
+  <si>
     <t>Die weltweit größten Sponsoren eigener imperialer Macht fordern die "Dekolonisierung" Russlands</t>
   </si>
   <si>
+    <t>article22120.txt</t>
+  </si>
+  <si>
     <t>Umverteilung ja, aber transparent</t>
   </si>
   <si>
+    <t>article2287.txt</t>
+  </si>
+  <si>
     <t>Ein gescheitertes Wachstumsmodell</t>
   </si>
   <si>
+    <t>article22144.txt</t>
+  </si>
+  <si>
     <t>Schluss mit den Masochismus-Übungen: Macht Nordstream II auf!</t>
   </si>
   <si>
+    <t>article22106.txt</t>
+  </si>
+  <si>
     <t>"CO₂-Kompensieren löst das Problem nicht"</t>
   </si>
   <si>
+    <t>article2224.txt</t>
+  </si>
+  <si>
     <t>Was die Europäer über Migration und Einwanderung wirklich denken</t>
   </si>
   <si>
+    <t>article26141.txt</t>
+  </si>
+  <si>
     <t>Aber Wissenschaft ist kein Dogma</t>
   </si>
   <si>
     <t>it</t>
   </si>
   <si>
+    <t>article26275.txt</t>
+  </si>
+  <si>
     <t>„Radikale schicke Umweltschützer“: Rampini kritisiert die Griechen und De Gregorio ist irritiert (Video)</t>
   </si>
   <si>
+    <t>article26106.txt</t>
+  </si>
+  <si>
     <t>G7 in München: Sie sind so unbedeutend, dass selbst die Demonstranten sich nicht mehr darum kümmern</t>
   </si>
   <si>
+    <t>article26272.txt</t>
+  </si>
+  <si>
     <t>Es ist das übliche Berlusconi: „Forza Italia bei 20 %, wir werden den Premierminister wählen.“ Über Überläufer: „Sie werden verschwinden wie Alfano“</t>
   </si>
   <si>
+    <t>article26293.txt</t>
+  </si>
+  <si>
     <t>Nachhaltiges Finanzwesen und EU-Taxonomie: Was ändert sich?</t>
   </si>
   <si>
+    <t>article26271.txt</t>
+  </si>
+  <si>
     <t>DRAGHI FÄLLT, PUTIN GENIEßT - GRAMELLINI: „ENTSCHULDIGUNG FÜR DAS BÖSSE DENKEN (ES WIRD DIE HITZE SEIN), ABER IN ANBETRACHT DER GEMEINSAMEN POSITION VON CONTE UND SALVINI ZUM KRIEG IST DAS WAHRE GEHEIMNIS NICHT, DASS DIE REGIERUNG GEFALLEN IST, SONDERN, WIE SIE ES GESCHAFFT HAT, BIS GESTERN DAUERZUHALTEN…“</t>
   </si>
   <si>
+    <t>article26134.txt</t>
+  </si>
+  <si>
     <t>Das Anti-Putin-Dilemma der deutschen Grünen: „Wie viele Minuten kann der Schauer dauern?“</t>
   </si>
   <si>
+    <t>article26187.txt</t>
+  </si>
+  <si>
     <t>Brasilien: Nein zu Sanktionen gegen Russland, sonst gibt es Welthunger. Die Realwirtschaft übertrifft die Papierwirtschaft</t>
   </si>
   <si>
+    <t>article26261.txt</t>
+  </si>
+  <si>
     <t>Die nächsten Alarme: heißer Herbst? Nein, sehr kalt</t>
   </si>
   <si>
+    <t>article2659.txt</t>
+  </si>
+  <si>
     <t>Covid und Impfstoff, Galli: Die Pflicht bleibt für über 50-Jährige bestehen. Keine Amnestie für Impfgegner</t>
   </si>
   <si>
+    <t>article26193.txt</t>
+  </si>
+  <si>
     <t>Russland-Ukraine-Krieg: Bolsonaros Brasilien bleibt neutral. Aber der Präsident ist pro-russisch</t>
   </si>
   <si>
+    <t>article2664.txt</t>
+  </si>
+  <si>
     <t>Affenpocken? Es ist rassistisch, es „diskriminiert Afrikaner“: Die WHO wird den Namen der Krankheit ändern</t>
   </si>
   <si>
+    <t>article26253.txt</t>
+  </si>
+  <si>
     <t>Türkischer Verteidigungsminister: Russland hatte nichts mit der Bombardierung von Odessa zu tun</t>
   </si>
   <si>
+    <t>article265.txt</t>
+  </si>
+  <si>
     <t>Fast 11.000 Migranten sind dieses Jahr bereits gelandet. Meloni: «Seeblockade ist die einzige Lösung»</t>
   </si>
   <si>
+    <t>article26300.txt</t>
+  </si>
+  <si>
     <t>„Lasst uns gemeinsam den Planeten retten“: Uns fehlte nur noch das Predigtbuch von Greta und dem Dalai Lama</t>
   </si>
   <si>
+    <t>article26301.txt</t>
+  </si>
+  <si>
     <t>Laut Moskau könnten die USA hinter Covid und den Affenpocken stecken</t>
   </si>
   <si>
+    <t>article2618.txt</t>
+  </si>
+  <si>
     <t>UkrLeaks: Nazis für den Export, von den USA nach Kiew</t>
   </si>
   <si>
+    <t>article26250.txt</t>
+  </si>
+  <si>
     <t>Energie: IEA, erste globale Krise, beschleunigt den Übergang</t>
   </si>
   <si>
+    <t>article26165.txt</t>
+  </si>
+  <si>
     <t>Salvini greift das Ius Scholae erneut an: „Echte Italiener sind Analphabeten“</t>
   </si>
   <si>
+    <t>article26294.txt</t>
+  </si>
+  <si>
     <t>Boomer einbinden Die Klimabewegung darf nicht nur eine Kindergeschichte bleiben</t>
   </si>
   <si>
+    <t>article26285.txt</t>
+  </si>
+  <si>
     <t>Die UN fordern Kiew, Moskau, die USA und die EU auf, die Abkommen über russischen und ukrainischen Weizen einzuhalten</t>
   </si>
   <si>
+    <t>article2656.txt</t>
+  </si>
+  <si>
     <t>Die Pause ist vorbei</t>
   </si>
   <si>
+    <t>article26121.txt</t>
+  </si>
+  <si>
     <t>„Affenpocken haben sich auf überraschende Weise verändert“</t>
   </si>
   <si>
+    <t>article2628.txt</t>
+  </si>
+  <si>
     <t>Wenn die Abstimmung irgendeinen Zweck hätte, würden die Anti-Vax-Leute es nicht zulassen.</t>
   </si>
   <si>
+    <t>article26172.txt</t>
+  </si>
+  <si>
     <t>Der Physiker Prodi gegen den Gretinismus: „Aber wie CO2 folgt auch die globale Erwärmung natürlichen Kreisläufen“</t>
   </si>
   <si>
+    <t>article26166.txt</t>
+  </si>
+  <si>
     <t>Achten Sie auf die Französischlektion. Er kann Italien auch etwas beibringen</t>
   </si>
   <si>
+    <t>article2687.txt</t>
+  </si>
+  <si>
     <t>Super-Umweltschützer Deutschland gezwungen, zur Kohle zurückzukehren.</t>
   </si>
   <si>
+    <t>article26212.txt</t>
+  </si>
+  <si>
     <t>Der „Preis“, den Russland für den Einsatz militärischer Gewalt zahlen muss</t>
   </si>
   <si>
+    <t>article26243.txt</t>
+  </si>
+  <si>
     <t>ZUR ABSTIMME! ZUR ABSTIMME! DIE SPRECHENDEN POLITIKER</t>
   </si>
   <si>
+    <t>article26295.txt</t>
+  </si>
+  <si>
     <t>Ukraine-EffektJetzt ist auch Island versucht, der EU beizutreten</t>
   </si>
   <si>
+    <t>article26136.txt</t>
+  </si>
+  <si>
     <t>Durch die Aufstände in Zentralasien strecken die Vereinigten Staaten ihre Tentakel Richtung Russland und China aus</t>
   </si>
   <si>
+    <t>article26192.txt</t>
+  </si>
+  <si>
     <t>Coronavirus, Bolsonaro: „In Italien sterben viele Menschen, weil es ein Land der alten Menschen ist“</t>
   </si>
   <si>
+    <t>article2667.txt</t>
+  </si>
+  <si>
     <t>Italien nutzt „humanitäre Korridore“, um Migranten aus Griechenland zu importieren</t>
   </si>
   <si>
+    <t>article2632.txt</t>
+  </si>
+  <si>
     <t>Migranten, die stille Invasion: Weitere 573 landeten in Augusta. Doch Lamorgese rührt keinen Finger</t>
   </si>
   <si>
+    <t>article268.txt</t>
+  </si>
+  <si>
     <t>Erich Vad, Merkels ehemaliger Berater: „USA und London können uns in den Dritten Weltkrieg hineinziehen“</t>
   </si>
   <si>
+    <t>article26242.txt</t>
+  </si>
+  <si>
     <t>1 – Trumps Kundgebung für die Wahlen in Alaska: „Mit Treibhauseffekt mehr Häuser mit Meerblick“</t>
   </si>
   <si>
+    <t>article26143.txt</t>
+  </si>
+  <si>
     <t>KLIMA: Die globale Erwärmung wird noch LANGE anhalten und das erste Opfer könnte der Mensch sein. Eine Studie verrät es</t>
   </si>
   <si>
+    <t>article26112.txt</t>
+  </si>
+  <si>
     <t>„The Great Game“ II: Britische Aktivitäten in der Ukraine</t>
   </si>
   <si>
+    <t>article26252.txt</t>
+  </si>
+  <si>
     <t>Deutschland, Wirtschaftsminister Habeck: „Wir stehen vor der größten Gaskrise“</t>
   </si>
   <si>
+    <t>article2620.txt</t>
+  </si>
+  <si>
     <t>Ecr, Fitto: EU-NATO kooperieren immer mehr, um die Auswahl der Länder zu gewährleisten, die dem Bündnis beitreten möchten</t>
   </si>
   <si>
+    <t>article26233.txt</t>
+  </si>
+  <si>
     <t>Hotspot Lampedusa kollabiert, Pisano: „Von der Regierung geschickte nutzlose Taxischiffe, wir sind die Einzigen, die die italienischen Grenzen verteidigen“</t>
   </si>
   <si>
+    <t>article26103.txt</t>
+  </si>
+  <si>
     <t>Der „Rat“ von EU-Kommission und IWF: Die Troika kehrt zurück, um Italien zu bedrohen</t>
   </si>
   <si>
+    <t>article2691.txt</t>
+  </si>
+  <si>
     <t>US-Plan scheitert in der Ukraine</t>
   </si>
   <si>
+    <t>article26211.txt</t>
+  </si>
+  <si>
     <t>Das „Insect Allies“-Programm – die Büchse der Pandora der DARPA</t>
   </si>
   <si>
+    <t>article26273.txt</t>
+  </si>
+  <si>
     <t>Wuhan, willkommener Lockdown: 1 Million Menschen wegen 4 asymptomatischen Fällen eingesperrt</t>
   </si>
   <si>
+    <t>article25171.txt</t>
+  </si>
+  <si>
     <t>in „Wiadomości“ TVP! Wie Tusk und die Deutschen „Quecksilber erfanden“</t>
   </si>
   <si>
     <t>po</t>
   </si>
   <si>
+    <t>article25150.txt</t>
+  </si>
+  <si>
     <t>Nicht Czarnek, nicht Najman, sondern Anna-Maria Żukowska. Der Linke-Abgeordnete gewann einen ungewöhnlichen Wettbewerb</t>
   </si>
   <si>
+    <t>article25132.txt</t>
+  </si>
+  <si>
     <t>Coronavirus. In Wuhan kommt es erneut zu einem Lockdown für Millionen Bürger. Es wurden vier Infektionsfälle festgestellt</t>
   </si>
   <si>
+    <t>article25167.txt</t>
+  </si>
+  <si>
     <t>Das Great Barrier Reef ist nicht nur wegen seines Namens großartig. Sie hat dem Klimawandel einfach die Stirn geboten</t>
   </si>
   <si>
+    <t>article253.txt</t>
+  </si>
+  <si>
     <t>Sylwia Spurek: Was gibt uns das Recht, eine Milchkuh auszubeuten?</t>
   </si>
   <si>
+    <t>article25165.txt</t>
+  </si>
+  <si>
     <t>VERSCHIEDENE FRONTEN EINES KRIEGES</t>
   </si>
   <si>
+    <t>article25131.txt</t>
+  </si>
+  <si>
     <t>Die Zahl der Coronavirus-Infektionen in Polen geht weiterhin nicht zurück. Neuer Bericht des Gesundheitsministeriums</t>
   </si>
   <si>
+    <t>article25188.txt</t>
+  </si>
+  <si>
     <t>Die meisten Polen wollen die Rückkehr der Corona-Beschränkungen nicht, die PiS-Wähler hingegen schon</t>
   </si>
   <si>
+    <t>article25119.txt</t>
+  </si>
+  <si>
     <t>In Polen wächst die Wut auf Deutschland. „Zu wenig, zu spät“</t>
   </si>
   <si>
+    <t>article25135.txt</t>
+  </si>
+  <si>
     <t>Polnische Ausgrabung</t>
   </si>
   <si>
+    <t>article25158.txt</t>
+  </si>
+  <si>
     <t>Eine kontroverse Meinung eines deutschen Politikers. „Nicht nur Russland, auch die USA sind böse“</t>
   </si>
   <si>
+    <t>article2526.txt</t>
+  </si>
+  <si>
     <t>Die Sanktionen des Westens wirken. Die russische Wirtschaft blutet</t>
   </si>
   <si>
+    <t>article25114.txt</t>
+  </si>
+  <si>
     <t>EU. Tusk erhielt jedoch einen „Befehl für Polen“</t>
   </si>
   <si>
+    <t>article2520.txt</t>
+  </si>
+  <si>
     <t>Ziobro zu Covid-Zertifikaten: Ich bin kein Unterstützer</t>
   </si>
   <si>
+    <t>article2597.txt</t>
+  </si>
+  <si>
     <t>Andrzej Duda ignoriert den verheerenden Klimabericht. Ihre Gedanken sind bei Antek Królikowskis Hochzeit</t>
   </si>
   <si>
+    <t>article2534.txt</t>
+  </si>
+  <si>
     <t>Duma-Sprecher: Das Arsenal westlicher Sanktionen ist erschöpft. Russland kann profitieren</t>
   </si>
   <si>
+    <t>article25104.txt</t>
+  </si>
+  <si>
     <t>Greta Thunberg. Ein atmosphärisches Symbol ohne Bedeutung [KOMMENTAR]</t>
   </si>
   <si>
+    <t>article2585.txt</t>
+  </si>
+  <si>
     <t>Legale Abtreibung. „Bei dieser Abstimmung war die Wahl sehr einfach, Sie sind entweder für Frauen oder dagegen.“</t>
   </si>
   <si>
+    <t>article2523.txt</t>
+  </si>
+  <si>
     <t>In Italien politisiert die extreme Rechte Impfgegner</t>
   </si>
   <si>
+    <t>article25163.txt</t>
+  </si>
+  <si>
     <t>Niedzielski: Die Ansteckungsgefahr von Affenpocken ist nicht hoch</t>
   </si>
   <si>
+    <t>article2533.txt</t>
+  </si>
+  <si>
     <t>Wolski: Für die Russen ist der Einsatz von Streubomben wie ein Brotholen</t>
   </si>
   <si>
+    <t>article25194.txt</t>
+  </si>
+  <si>
     <t>"Heuchelei". Macron steht unter Beschuss, nachdem er Urlaubsfotos enthüllt hat</t>
   </si>
   <si>
+    <t>article25122.txt</t>
+  </si>
+  <si>
     <t>„Selenskys Industrie“ schweigt über den Krieg. Die Ukraine nimmt es Satirikern aus Russland übel, weil sie Putin nicht verurteilen</t>
   </si>
   <si>
+    <t>article2598.txt</t>
+  </si>
+  <si>
     <t>Der Kolonialismus ist immer noch im Gange. Und es ist eine der Ursachen des Klimawandels</t>
   </si>
   <si>
+    <t>article25110.txt</t>
+  </si>
+  <si>
     <t>In Südafrika haben sie bereits das Licht ausgeschaltet</t>
   </si>
   <si>
+    <t>article251.txt</t>
+  </si>
+  <si>
     <t>Nord Stream 2 ist das größte Problem der deutschen Politik</t>
   </si>
   <si>
+    <t>article25168.txt</t>
+  </si>
+  <si>
     <t>Kim Jong Un will Putins Armee unterstützen. Über diese Ausrüstung verfügt Nordkorea.</t>
   </si>
   <si>
+    <t>article25189.txt</t>
+  </si>
+  <si>
     <t>Kommt eine weitere Welle von Beschränkungen?</t>
+  </si>
+  <si>
+    <t>article2542.txt</t>
   </si>
   <si>
     <t>Über hundert Coronavirus-Infektionen im Zusammenhang mit einem Riegel. „Gefährliche Welle“ in Peking</t>
@@ -1052,10 +1685,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P211"/>
+  <dimension ref="A1:Q211"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1104,1685 +1737,2318 @@
       <c r="P1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="C2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+      <c r="C3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+      <c r="C4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+      <c r="C5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="B6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+      <c r="C6" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+      <c r="C7" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="B8" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+      <c r="C8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="B9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+      <c r="C9" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="B10" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+      <c r="C10" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="B11" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+      <c r="C11" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="B12" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+      <c r="C12" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="B13" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+      <c r="C13" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="B14" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+        <v>43</v>
+      </c>
+      <c r="C14" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="B15" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+        <v>45</v>
+      </c>
+      <c r="C15" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="B16" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+        <v>47</v>
+      </c>
+      <c r="C16" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="B17" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+        <v>49</v>
+      </c>
+      <c r="C17" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="B18" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+        <v>51</v>
+      </c>
+      <c r="C18" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="B19" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+        <v>53</v>
+      </c>
+      <c r="C19" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="B20" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+        <v>55</v>
+      </c>
+      <c r="C20" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="B21" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+        <v>57</v>
+      </c>
+      <c r="C21" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>37</v>
+        <v>58</v>
       </c>
       <c r="B22" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+        <v>59</v>
+      </c>
+      <c r="C22" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="B23" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+        <v>61</v>
+      </c>
+      <c r="C23" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="B24" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+      <c r="C24" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>40</v>
+        <v>64</v>
       </c>
       <c r="B25" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+      <c r="C25" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>41</v>
+        <v>66</v>
       </c>
       <c r="B26" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+        <v>67</v>
+      </c>
+      <c r="C26" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>42</v>
+        <v>68</v>
       </c>
       <c r="B27" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+        <v>69</v>
+      </c>
+      <c r="C27" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="B28" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+        <v>71</v>
+      </c>
+      <c r="C28" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>44</v>
+        <v>72</v>
       </c>
       <c r="B29" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+        <v>73</v>
+      </c>
+      <c r="C29" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>45</v>
+        <v>74</v>
       </c>
       <c r="B30" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+        <v>75</v>
+      </c>
+      <c r="C30" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>46</v>
+        <v>76</v>
       </c>
       <c r="B31" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+      <c r="C31" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>47</v>
+        <v>78</v>
       </c>
       <c r="B32" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+        <v>79</v>
+      </c>
+      <c r="C32" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>48</v>
+        <v>80</v>
       </c>
       <c r="B33" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+        <v>81</v>
+      </c>
+      <c r="C33" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>49</v>
+        <v>82</v>
       </c>
       <c r="B34" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+        <v>83</v>
+      </c>
+      <c r="C34" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>50</v>
+        <v>84</v>
       </c>
       <c r="B35" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+        <v>85</v>
+      </c>
+      <c r="C35" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>51</v>
+        <v>86</v>
       </c>
       <c r="B36" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+        <v>87</v>
+      </c>
+      <c r="C36" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>52</v>
+        <v>88</v>
       </c>
       <c r="B37" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+        <v>89</v>
+      </c>
+      <c r="C37" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>53</v>
+        <v>90</v>
       </c>
       <c r="B38" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+        <v>91</v>
+      </c>
+      <c r="C38" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>54</v>
+        <v>92</v>
       </c>
       <c r="B39" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+        <v>93</v>
+      </c>
+      <c r="C39" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="B40" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+        <v>95</v>
+      </c>
+      <c r="C40" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>56</v>
+        <v>96</v>
       </c>
       <c r="B41" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+      <c r="C41" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>57</v>
+        <v>98</v>
       </c>
       <c r="B42" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+        <v>99</v>
+      </c>
+      <c r="C42" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>58</v>
+        <v>100</v>
       </c>
       <c r="B43" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+        <v>101</v>
+      </c>
+      <c r="C43" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>59</v>
+        <v>102</v>
       </c>
       <c r="B44" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+        <v>103</v>
+      </c>
+      <c r="C44" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>60</v>
+        <v>104</v>
       </c>
       <c r="B45" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+        <v>105</v>
+      </c>
+      <c r="C45" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>61</v>
+        <v>106</v>
       </c>
       <c r="B46" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+        <v>107</v>
+      </c>
+      <c r="C46" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>62</v>
+        <v>108</v>
       </c>
       <c r="B47" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+      <c r="C47" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>63</v>
+        <v>110</v>
       </c>
       <c r="B48" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+        <v>111</v>
+      </c>
+      <c r="C48" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>64</v>
+        <v>112</v>
       </c>
       <c r="B49" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+        <v>113</v>
+      </c>
+      <c r="C49" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>65</v>
+        <v>114</v>
       </c>
       <c r="B50" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+        <v>115</v>
+      </c>
+      <c r="C50" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>66</v>
+        <v>116</v>
       </c>
       <c r="B51" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+        <v>117</v>
+      </c>
+      <c r="C51" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>67</v>
+        <v>118</v>
       </c>
       <c r="B52" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+        <v>119</v>
+      </c>
+      <c r="C52" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>68</v>
+        <v>120</v>
       </c>
       <c r="B53" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+        <v>121</v>
+      </c>
+      <c r="C53" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>69</v>
+        <v>122</v>
       </c>
       <c r="B54" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+        <v>123</v>
+      </c>
+      <c r="C54" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>70</v>
+        <v>124</v>
       </c>
       <c r="B55" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+        <v>125</v>
+      </c>
+      <c r="C55" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>71</v>
+        <v>126</v>
       </c>
       <c r="B56" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+        <v>127</v>
+      </c>
+      <c r="C56" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>72</v>
+        <v>128</v>
       </c>
       <c r="B57" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+        <v>129</v>
+      </c>
+      <c r="C57" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>73</v>
+        <v>130</v>
       </c>
       <c r="B58" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+        <v>131</v>
+      </c>
+      <c r="C58" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>74</v>
+        <v>132</v>
       </c>
       <c r="B59" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+        <v>133</v>
+      </c>
+      <c r="C59" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>75</v>
+        <v>134</v>
       </c>
       <c r="B60" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+        <v>135</v>
+      </c>
+      <c r="C60" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>76</v>
+        <v>136</v>
       </c>
       <c r="B61" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+        <v>137</v>
+      </c>
+      <c r="C61" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>77</v>
+        <v>138</v>
       </c>
       <c r="B62" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+        <v>139</v>
+      </c>
+      <c r="C62" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>78</v>
+        <v>140</v>
       </c>
       <c r="B63" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+        <v>141</v>
+      </c>
+      <c r="C63" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>79</v>
+        <v>142</v>
       </c>
       <c r="B64" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+        <v>143</v>
+      </c>
+      <c r="C64" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>80</v>
+        <v>144</v>
       </c>
       <c r="B65" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+        <v>145</v>
+      </c>
+      <c r="C65" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>81</v>
+        <v>146</v>
       </c>
       <c r="B66" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+        <v>147</v>
+      </c>
+      <c r="C66" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>82</v>
+        <v>148</v>
       </c>
       <c r="B67" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+        <v>149</v>
+      </c>
+      <c r="C67" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>83</v>
+        <v>150</v>
       </c>
       <c r="B68" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+        <v>151</v>
+      </c>
+      <c r="C68" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>84</v>
+        <v>152</v>
       </c>
       <c r="B69" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+        <v>153</v>
+      </c>
+      <c r="C69" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>85</v>
+        <v>154</v>
       </c>
       <c r="B70" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+        <v>155</v>
+      </c>
+      <c r="C70" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>86</v>
+        <v>156</v>
       </c>
       <c r="B71" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+        <v>157</v>
+      </c>
+      <c r="C71" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>87</v>
+        <v>158</v>
       </c>
       <c r="B72" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+        <v>159</v>
+      </c>
+      <c r="C72" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>88</v>
+        <v>160</v>
       </c>
       <c r="B73" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+        <v>161</v>
+      </c>
+      <c r="C73" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>89</v>
+        <v>162</v>
       </c>
       <c r="B74" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+        <v>163</v>
+      </c>
+      <c r="C74" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>90</v>
+        <v>164</v>
       </c>
       <c r="B75" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+        <v>165</v>
+      </c>
+      <c r="C75" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>91</v>
+        <v>166</v>
       </c>
       <c r="B76" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+        <v>167</v>
+      </c>
+      <c r="C76" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>92</v>
+        <v>168</v>
       </c>
       <c r="B77" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+        <v>169</v>
+      </c>
+      <c r="C77" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>93</v>
+        <v>170</v>
       </c>
       <c r="B78" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
+        <v>171</v>
+      </c>
+      <c r="C78" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>94</v>
+        <v>172</v>
       </c>
       <c r="B79" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
+        <v>173</v>
+      </c>
+      <c r="C79" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>96</v>
+        <v>175</v>
       </c>
       <c r="B80" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
+        <v>176</v>
+      </c>
+      <c r="C80" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>97</v>
+        <v>177</v>
       </c>
       <c r="B81" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
+        <v>178</v>
+      </c>
+      <c r="C81" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>98</v>
+        <v>179</v>
       </c>
       <c r="B82" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
+        <v>180</v>
+      </c>
+      <c r="C82" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>99</v>
+        <v>181</v>
       </c>
       <c r="B83" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
+        <v>182</v>
+      </c>
+      <c r="C83" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>100</v>
+        <v>183</v>
       </c>
       <c r="B84" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
+        <v>184</v>
+      </c>
+      <c r="C84" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>101</v>
+        <v>185</v>
       </c>
       <c r="B85" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
+        <v>186</v>
+      </c>
+      <c r="C85" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>102</v>
+        <v>187</v>
       </c>
       <c r="B86" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
+        <v>188</v>
+      </c>
+      <c r="C86" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>103</v>
+        <v>189</v>
       </c>
       <c r="B87" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
+        <v>190</v>
+      </c>
+      <c r="C87" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>104</v>
+        <v>191</v>
       </c>
       <c r="B88" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
+        <v>192</v>
+      </c>
+      <c r="C88" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>105</v>
+        <v>193</v>
       </c>
       <c r="B89" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
+        <v>194</v>
+      </c>
+      <c r="C89" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>106</v>
+        <v>195</v>
       </c>
       <c r="B90" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
+        <v>196</v>
+      </c>
+      <c r="C90" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>107</v>
+        <v>197</v>
       </c>
       <c r="B91" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
+        <v>198</v>
+      </c>
+      <c r="C91" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>108</v>
+        <v>199</v>
       </c>
       <c r="B92" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
+        <v>200</v>
+      </c>
+      <c r="C92" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>109</v>
+        <v>201</v>
       </c>
       <c r="B93" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
+        <v>202</v>
+      </c>
+      <c r="C93" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>110</v>
+        <v>203</v>
       </c>
       <c r="B94" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
+        <v>204</v>
+      </c>
+      <c r="C94" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>111</v>
+        <v>205</v>
       </c>
       <c r="B95" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
+        <v>206</v>
+      </c>
+      <c r="C95" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>112</v>
+        <v>207</v>
       </c>
       <c r="B96" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
+        <v>208</v>
+      </c>
+      <c r="C96" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>113</v>
+        <v>209</v>
       </c>
       <c r="B97" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
+        <v>210</v>
+      </c>
+      <c r="C97" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>114</v>
+        <v>211</v>
       </c>
       <c r="B98" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
+        <v>212</v>
+      </c>
+      <c r="C98" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>115</v>
+        <v>213</v>
       </c>
       <c r="B99" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
+        <v>214</v>
+      </c>
+      <c r="C99" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>116</v>
+        <v>215</v>
       </c>
       <c r="B100" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
+        <v>216</v>
+      </c>
+      <c r="C100" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>117</v>
+        <v>217</v>
       </c>
       <c r="B101" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
+        <v>218</v>
+      </c>
+      <c r="C101" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>118</v>
+        <v>219</v>
       </c>
       <c r="B102" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
+        <v>220</v>
+      </c>
+      <c r="C102" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>119</v>
+        <v>221</v>
       </c>
       <c r="B103" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+      <c r="C103" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>120</v>
+        <v>223</v>
       </c>
       <c r="B104" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
+        <v>224</v>
+      </c>
+      <c r="C104" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>121</v>
+        <v>225</v>
       </c>
       <c r="B105" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
+        <v>226</v>
+      </c>
+      <c r="C105" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>122</v>
+        <v>227</v>
       </c>
       <c r="B106" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
+        <v>228</v>
+      </c>
+      <c r="C106" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>123</v>
+        <v>229</v>
       </c>
       <c r="B107" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.25">
+        <v>230</v>
+      </c>
+      <c r="C107" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>124</v>
+        <v>231</v>
       </c>
       <c r="B108" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
+        <v>232</v>
+      </c>
+      <c r="C108" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>125</v>
+        <v>233</v>
       </c>
       <c r="B109" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.25">
+        <v>234</v>
+      </c>
+      <c r="C109" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>126</v>
+        <v>235</v>
       </c>
       <c r="B110" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.25">
+        <v>236</v>
+      </c>
+      <c r="C110" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>127</v>
+        <v>237</v>
       </c>
       <c r="B111" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.25">
+        <v>238</v>
+      </c>
+      <c r="C111" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>129</v>
+        <v>240</v>
       </c>
       <c r="B112" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.25">
+        <v>241</v>
+      </c>
+      <c r="C112" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>130</v>
+        <v>242</v>
       </c>
       <c r="B113" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.25">
+        <v>243</v>
+      </c>
+      <c r="C113" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>131</v>
+        <v>244</v>
       </c>
       <c r="B114" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.25">
+        <v>245</v>
+      </c>
+      <c r="C114" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>132</v>
+        <v>246</v>
       </c>
       <c r="B115" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+      <c r="C115" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>133</v>
+        <v>248</v>
       </c>
       <c r="B116" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.25">
+        <v>249</v>
+      </c>
+      <c r="C116" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>134</v>
+        <v>250</v>
       </c>
       <c r="B117" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.25">
+        <v>251</v>
+      </c>
+      <c r="C117" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>135</v>
+        <v>252</v>
       </c>
       <c r="B118" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.25">
+        <v>253</v>
+      </c>
+      <c r="C118" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>136</v>
+        <v>254</v>
       </c>
       <c r="B119" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.25">
+        <v>255</v>
+      </c>
+      <c r="C119" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>137</v>
+        <v>256</v>
       </c>
       <c r="B120" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.25">
+        <v>257</v>
+      </c>
+      <c r="C120" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>138</v>
+        <v>258</v>
       </c>
       <c r="B121" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.25">
+        <v>259</v>
+      </c>
+      <c r="C121" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>139</v>
+        <v>260</v>
       </c>
       <c r="B122" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.25">
+        <v>261</v>
+      </c>
+      <c r="C122" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>140</v>
+        <v>262</v>
       </c>
       <c r="B123" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.25">
+        <v>263</v>
+      </c>
+      <c r="C123" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>141</v>
+        <v>264</v>
       </c>
       <c r="B124" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.25">
+        <v>265</v>
+      </c>
+      <c r="C124" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>142</v>
+        <v>266</v>
       </c>
       <c r="B125" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.25">
+        <v>267</v>
+      </c>
+      <c r="C125" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>143</v>
+        <v>268</v>
       </c>
       <c r="B126" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="127" spans="1:2" x14ac:dyDescent="0.25">
+        <v>269</v>
+      </c>
+      <c r="C126" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>144</v>
+        <v>270</v>
       </c>
       <c r="B127" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="128" spans="1:2" x14ac:dyDescent="0.25">
+        <v>271</v>
+      </c>
+      <c r="C127" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>145</v>
+        <v>272</v>
       </c>
       <c r="B128" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.25">
+        <v>273</v>
+      </c>
+      <c r="C128" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>146</v>
+        <v>274</v>
       </c>
       <c r="B129" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.25">
+        <v>275</v>
+      </c>
+      <c r="C129" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>147</v>
+        <v>276</v>
       </c>
       <c r="B130" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.25">
+        <v>277</v>
+      </c>
+      <c r="C130" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>148</v>
+        <v>278</v>
       </c>
       <c r="B131" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.25">
+        <v>279</v>
+      </c>
+      <c r="C131" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>149</v>
+        <v>280</v>
       </c>
       <c r="B132" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.25">
+        <v>281</v>
+      </c>
+      <c r="C132" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>150</v>
+        <v>282</v>
       </c>
       <c r="B133" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.25">
+        <v>283</v>
+      </c>
+      <c r="C133" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>151</v>
+        <v>284</v>
       </c>
       <c r="B134" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.25">
+        <v>285</v>
+      </c>
+      <c r="C134" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>152</v>
+        <v>286</v>
       </c>
       <c r="B135" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="136" spans="1:2" x14ac:dyDescent="0.25">
+        <v>287</v>
+      </c>
+      <c r="C135" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>153</v>
+        <v>288</v>
       </c>
       <c r="B136" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="137" spans="1:2" x14ac:dyDescent="0.25">
+        <v>289</v>
+      </c>
+      <c r="C136" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>154</v>
+        <v>290</v>
       </c>
       <c r="B137" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="138" spans="1:2" x14ac:dyDescent="0.25">
+        <v>291</v>
+      </c>
+      <c r="C137" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>155</v>
+        <v>292</v>
       </c>
       <c r="B138" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="139" spans="1:2" x14ac:dyDescent="0.25">
+        <v>293</v>
+      </c>
+      <c r="C138" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>157</v>
+        <v>295</v>
       </c>
       <c r="B139" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="140" spans="1:2" x14ac:dyDescent="0.25">
+        <v>296</v>
+      </c>
+      <c r="C139" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>158</v>
+        <v>297</v>
       </c>
       <c r="B140" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="141" spans="1:2" x14ac:dyDescent="0.25">
+        <v>298</v>
+      </c>
+      <c r="C140" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>159</v>
+        <v>299</v>
       </c>
       <c r="B141" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="142" spans="1:2" x14ac:dyDescent="0.25">
+        <v>300</v>
+      </c>
+      <c r="C141" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>160</v>
+        <v>301</v>
       </c>
       <c r="B142" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="143" spans="1:2" x14ac:dyDescent="0.25">
+        <v>302</v>
+      </c>
+      <c r="C142" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>161</v>
+        <v>303</v>
       </c>
       <c r="B143" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="144" spans="1:2" x14ac:dyDescent="0.25">
+        <v>304</v>
+      </c>
+      <c r="C143" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>162</v>
+        <v>305</v>
       </c>
       <c r="B144" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.25">
+        <v>306</v>
+      </c>
+      <c r="C144" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>163</v>
+        <v>307</v>
       </c>
       <c r="B145" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="146" spans="1:2" x14ac:dyDescent="0.25">
+        <v>308</v>
+      </c>
+      <c r="C145" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>164</v>
+        <v>309</v>
       </c>
       <c r="B146" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="147" spans="1:2" x14ac:dyDescent="0.25">
+        <v>310</v>
+      </c>
+      <c r="C146" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>165</v>
+        <v>311</v>
       </c>
       <c r="B147" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="148" spans="1:2" x14ac:dyDescent="0.25">
+        <v>312</v>
+      </c>
+      <c r="C147" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>166</v>
+        <v>313</v>
       </c>
       <c r="B148" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="149" spans="1:2" x14ac:dyDescent="0.25">
+        <v>314</v>
+      </c>
+      <c r="C148" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>167</v>
+        <v>315</v>
       </c>
       <c r="B149" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="150" spans="1:2" x14ac:dyDescent="0.25">
+        <v>316</v>
+      </c>
+      <c r="C149" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>168</v>
+        <v>317</v>
       </c>
       <c r="B150" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="151" spans="1:2" x14ac:dyDescent="0.25">
+        <v>318</v>
+      </c>
+      <c r="C150" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>169</v>
+        <v>319</v>
       </c>
       <c r="B151" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="152" spans="1:2" x14ac:dyDescent="0.25">
+        <v>320</v>
+      </c>
+      <c r="C151" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>170</v>
+        <v>321</v>
       </c>
       <c r="B152" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="153" spans="1:2" x14ac:dyDescent="0.25">
+        <v>322</v>
+      </c>
+      <c r="C152" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>171</v>
+        <v>323</v>
       </c>
       <c r="B153" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="154" spans="1:2" x14ac:dyDescent="0.25">
+        <v>324</v>
+      </c>
+      <c r="C153" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>172</v>
+        <v>325</v>
       </c>
       <c r="B154" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="155" spans="1:2" x14ac:dyDescent="0.25">
+        <v>326</v>
+      </c>
+      <c r="C154" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>173</v>
+        <v>327</v>
       </c>
       <c r="B155" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="156" spans="1:2" x14ac:dyDescent="0.25">
+        <v>328</v>
+      </c>
+      <c r="C155" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>174</v>
+        <v>329</v>
       </c>
       <c r="B156" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="157" spans="1:2" x14ac:dyDescent="0.25">
+        <v>330</v>
+      </c>
+      <c r="C156" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>175</v>
+        <v>331</v>
       </c>
       <c r="B157" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="158" spans="1:2" x14ac:dyDescent="0.25">
+        <v>332</v>
+      </c>
+      <c r="C157" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>176</v>
+        <v>333</v>
       </c>
       <c r="B158" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="159" spans="1:2" x14ac:dyDescent="0.25">
+        <v>334</v>
+      </c>
+      <c r="C158" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>177</v>
+        <v>335</v>
       </c>
       <c r="B159" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="160" spans="1:2" x14ac:dyDescent="0.25">
+        <v>336</v>
+      </c>
+      <c r="C159" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>178</v>
+        <v>337</v>
       </c>
       <c r="B160" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="161" spans="1:2" x14ac:dyDescent="0.25">
+        <v>338</v>
+      </c>
+      <c r="C160" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>179</v>
+        <v>339</v>
       </c>
       <c r="B161" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="162" spans="1:2" x14ac:dyDescent="0.25">
+        <v>340</v>
+      </c>
+      <c r="C161" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>180</v>
+        <v>341</v>
       </c>
       <c r="B162" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="163" spans="1:2" x14ac:dyDescent="0.25">
+        <v>342</v>
+      </c>
+      <c r="C162" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>181</v>
+        <v>343</v>
       </c>
       <c r="B163" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="164" spans="1:2" x14ac:dyDescent="0.25">
+        <v>344</v>
+      </c>
+      <c r="C163" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>182</v>
+        <v>345</v>
       </c>
       <c r="B164" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="165" spans="1:2" x14ac:dyDescent="0.25">
+        <v>346</v>
+      </c>
+      <c r="C164" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>183</v>
+        <v>347</v>
       </c>
       <c r="B165" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="166" spans="1:2" x14ac:dyDescent="0.25">
+        <v>348</v>
+      </c>
+      <c r="C165" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>184</v>
+        <v>349</v>
       </c>
       <c r="B166" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="167" spans="1:2" x14ac:dyDescent="0.25">
+        <v>350</v>
+      </c>
+      <c r="C166" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>185</v>
+        <v>351</v>
       </c>
       <c r="B167" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="168" spans="1:2" x14ac:dyDescent="0.25">
+        <v>352</v>
+      </c>
+      <c r="C167" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>186</v>
+        <v>353</v>
       </c>
       <c r="B168" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="169" spans="1:2" x14ac:dyDescent="0.25">
+        <v>354</v>
+      </c>
+      <c r="C168" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>187</v>
+        <v>355</v>
       </c>
       <c r="B169" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="170" spans="1:2" x14ac:dyDescent="0.25">
+        <v>356</v>
+      </c>
+      <c r="C169" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>188</v>
+        <v>357</v>
       </c>
       <c r="B170" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="171" spans="1:2" x14ac:dyDescent="0.25">
+        <v>358</v>
+      </c>
+      <c r="C170" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>189</v>
+        <v>359</v>
       </c>
       <c r="B171" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="172" spans="1:2" x14ac:dyDescent="0.25">
+        <v>360</v>
+      </c>
+      <c r="C171" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>190</v>
+        <v>361</v>
       </c>
       <c r="B172" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="173" spans="1:2" x14ac:dyDescent="0.25">
+        <v>362</v>
+      </c>
+      <c r="C172" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>191</v>
+        <v>363</v>
       </c>
       <c r="B173" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="174" spans="1:2" x14ac:dyDescent="0.25">
+        <v>364</v>
+      </c>
+      <c r="C173" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>192</v>
+        <v>365</v>
       </c>
       <c r="B174" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="175" spans="1:2" x14ac:dyDescent="0.25">
+        <v>366</v>
+      </c>
+      <c r="C174" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>193</v>
+        <v>367</v>
       </c>
       <c r="B175" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="176" spans="1:2" x14ac:dyDescent="0.25">
+        <v>368</v>
+      </c>
+      <c r="C175" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>194</v>
+        <v>369</v>
       </c>
       <c r="B176" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="177" spans="1:2" x14ac:dyDescent="0.25">
+        <v>370</v>
+      </c>
+      <c r="C176" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>195</v>
+        <v>371</v>
       </c>
       <c r="B177" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="178" spans="1:2" x14ac:dyDescent="0.25">
+        <v>372</v>
+      </c>
+      <c r="C177" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>196</v>
+        <v>373</v>
       </c>
       <c r="B178" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="179" spans="1:2" x14ac:dyDescent="0.25">
+        <v>374</v>
+      </c>
+      <c r="C178" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>197</v>
+        <v>375</v>
       </c>
       <c r="B179" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="180" spans="1:2" x14ac:dyDescent="0.25">
+        <v>376</v>
+      </c>
+      <c r="C179" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>198</v>
+        <v>377</v>
       </c>
       <c r="B180" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="181" spans="1:2" x14ac:dyDescent="0.25">
+        <v>378</v>
+      </c>
+      <c r="C180" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>199</v>
+        <v>379</v>
       </c>
       <c r="B181" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="182" spans="1:2" x14ac:dyDescent="0.25">
+        <v>380</v>
+      </c>
+      <c r="C181" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>200</v>
+        <v>381</v>
       </c>
       <c r="B182" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="183" spans="1:2" x14ac:dyDescent="0.25">
+        <v>382</v>
+      </c>
+      <c r="C182" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>201</v>
+        <v>383</v>
       </c>
       <c r="B183" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="184" spans="1:2" x14ac:dyDescent="0.25">
+        <v>384</v>
+      </c>
+      <c r="C183" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>203</v>
+        <v>386</v>
       </c>
       <c r="B184" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="185" spans="1:2" x14ac:dyDescent="0.25">
+        <v>387</v>
+      </c>
+      <c r="C184" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>204</v>
+        <v>388</v>
       </c>
       <c r="B185" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="186" spans="1:2" x14ac:dyDescent="0.25">
+        <v>389</v>
+      </c>
+      <c r="C185" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>205</v>
+        <v>390</v>
       </c>
       <c r="B186" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="187" spans="1:2" x14ac:dyDescent="0.25">
+        <v>391</v>
+      </c>
+      <c r="C186" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>206</v>
+        <v>392</v>
       </c>
       <c r="B187" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="188" spans="1:2" x14ac:dyDescent="0.25">
+        <v>393</v>
+      </c>
+      <c r="C187" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="188" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>207</v>
+        <v>394</v>
       </c>
       <c r="B188" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="189" spans="1:2" x14ac:dyDescent="0.25">
+        <v>395</v>
+      </c>
+      <c r="C188" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="189" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>208</v>
+        <v>396</v>
       </c>
       <c r="B189" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="190" spans="1:2" x14ac:dyDescent="0.25">
+        <v>397</v>
+      </c>
+      <c r="C189" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="190" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>209</v>
+        <v>398</v>
       </c>
       <c r="B190" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="191" spans="1:2" x14ac:dyDescent="0.25">
+        <v>399</v>
+      </c>
+      <c r="C190" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="191" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>210</v>
+        <v>400</v>
       </c>
       <c r="B191" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="192" spans="1:2" x14ac:dyDescent="0.25">
+        <v>401</v>
+      </c>
+      <c r="C191" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="192" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>211</v>
+        <v>402</v>
       </c>
       <c r="B192" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="193" spans="1:2" x14ac:dyDescent="0.25">
+        <v>403</v>
+      </c>
+      <c r="C192" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>212</v>
+        <v>404</v>
       </c>
       <c r="B193" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="194" spans="1:2" x14ac:dyDescent="0.25">
+        <v>405</v>
+      </c>
+      <c r="C193" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>213</v>
+        <v>406</v>
       </c>
       <c r="B194" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="195" spans="1:2" x14ac:dyDescent="0.25">
+        <v>407</v>
+      </c>
+      <c r="C194" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>214</v>
+        <v>408</v>
       </c>
       <c r="B195" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="196" spans="1:2" x14ac:dyDescent="0.25">
+        <v>409</v>
+      </c>
+      <c r="C195" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>215</v>
+        <v>410</v>
       </c>
       <c r="B196" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="197" spans="1:2" x14ac:dyDescent="0.25">
+        <v>411</v>
+      </c>
+      <c r="C196" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>216</v>
+        <v>412</v>
       </c>
       <c r="B197" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="198" spans="1:2" x14ac:dyDescent="0.25">
+        <v>413</v>
+      </c>
+      <c r="C197" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="198" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>217</v>
+        <v>414</v>
       </c>
       <c r="B198" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="199" spans="1:2" x14ac:dyDescent="0.25">
+        <v>415</v>
+      </c>
+      <c r="C198" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>218</v>
+        <v>416</v>
       </c>
       <c r="B199" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="200" spans="1:2" x14ac:dyDescent="0.25">
+        <v>417</v>
+      </c>
+      <c r="C199" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>219</v>
+        <v>418</v>
       </c>
       <c r="B200" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="201" spans="1:2" x14ac:dyDescent="0.25">
+        <v>419</v>
+      </c>
+      <c r="C200" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="201" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>220</v>
+        <v>420</v>
       </c>
       <c r="B201" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="202" spans="1:2" x14ac:dyDescent="0.25">
+        <v>421</v>
+      </c>
+      <c r="C201" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="202" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>221</v>
+        <v>422</v>
       </c>
       <c r="B202" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="203" spans="1:2" x14ac:dyDescent="0.25">
+        <v>423</v>
+      </c>
+      <c r="C202" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="203" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>222</v>
+        <v>424</v>
       </c>
       <c r="B203" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="204" spans="1:2" x14ac:dyDescent="0.25">
+        <v>425</v>
+      </c>
+      <c r="C203" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="204" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>223</v>
+        <v>426</v>
       </c>
       <c r="B204" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="205" spans="1:2" x14ac:dyDescent="0.25">
+        <v>427</v>
+      </c>
+      <c r="C204" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>224</v>
+        <v>428</v>
       </c>
       <c r="B205" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="206" spans="1:2" x14ac:dyDescent="0.25">
+        <v>429</v>
+      </c>
+      <c r="C205" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>225</v>
+        <v>430</v>
       </c>
       <c r="B206" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="207" spans="1:2" x14ac:dyDescent="0.25">
+        <v>431</v>
+      </c>
+      <c r="C206" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="207" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>226</v>
+        <v>432</v>
       </c>
       <c r="B207" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="208" spans="1:2" x14ac:dyDescent="0.25">
+        <v>433</v>
+      </c>
+      <c r="C207" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="208" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>227</v>
+        <v>434</v>
       </c>
       <c r="B208" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="209" spans="1:2" x14ac:dyDescent="0.25">
+        <v>435</v>
+      </c>
+      <c r="C208" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="209" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>228</v>
+        <v>436</v>
       </c>
       <c r="B209" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="210" spans="1:2" x14ac:dyDescent="0.25">
+        <v>437</v>
+      </c>
+      <c r="C209" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="210" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>229</v>
+        <v>438</v>
       </c>
       <c r="B210" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="211" spans="1:2" x14ac:dyDescent="0.25">
+        <v>439</v>
+      </c>
+      <c r="C210" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="211" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>230</v>
+        <v>440</v>
       </c>
       <c r="B211" t="s">
-        <v>202</v>
+        <v>441</v>
+      </c>
+      <c r="C211" t="s">
+        <v>385</v>
       </c>
     </row>
   </sheetData>
